--- a/results/format_issue.xlsx
+++ b/results/format_issue.xlsx
@@ -4677,7 +4677,7 @@
         <f>1245.3</f>
         <v>1245.3</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="22">
         <f>779.52</f>
         <v>779.52</v>
       </c>
@@ -6034,7 +6034,7 @@
         <f>1116.53</f>
         <v>1116.53</v>
       </c>
-      <c r="G94" s="23">
+      <c r="G94" s="22">
         <f>679.45</f>
         <v>679.45</v>
       </c>
